--- a/output/pdf_financials_xlsx/TSK.xlsx
+++ b/output/pdf_financials_xlsx/TSK.xlsx
@@ -1271,19 +1271,19 @@
         <v>-5.912546</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-5.48</v>
+        <v>-80.867796</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-8.622999999999999</v>
+        <v>-46.689722</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-1.951</v>
+        <v>-27.234178</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0.498</v>
+        <v>-29.028788</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0</v>
+        <v>-41.612586</v>
       </c>
     </row>
     <row r="18">
@@ -1487,19 +1487,19 @@
         <v>-8.872078999999999</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>37.693898</v>
+        <v>-37.693898</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>19.033361</v>
+        <v>-19.033361</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>12.641589</v>
+        <v>-12.641589</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>14.265394</v>
+        <v>-14.265394</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>20.806293</v>
+        <v>-20.806293</v>
       </c>
     </row>
     <row r="21">
@@ -1643,19 +1643,19 @@
         <v>-8.872078999999999</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>37.693898</v>
+        <v>-37.693898</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>19.033361</v>
+        <v>-19.033361</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>12.641589</v>
+        <v>-12.641589</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>14.265394</v>
+        <v>-14.265394</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>20.806293</v>
+        <v>-20.806293</v>
       </c>
     </row>
     <row r="24">
@@ -1817,19 +1817,19 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>251.292653</v>
+        <v>-251.292653</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>67.97628899999999</v>
+        <v>-67.97628899999999</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>79.00993099999999</v>
+        <v>-79.00993099999999</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>95.102627</v>
+        <v>-95.102627</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>130.039331</v>
+        <v>-130.039331</v>
       </c>
     </row>
     <row r="27">
@@ -2087,19 +2087,19 @@
         <v>-199.7796949721459</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>12.69285437233395</v>
+        <v>187.307145627666</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>31.17908390044518</v>
+        <v>168.8209160995548</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>13.36980024586453</v>
+        <v>186.6301997541355</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>3.373208084807599</v>
+        <v>196.6267919151924</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32">
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>164.8091481334237</v>
+        <v>-164.8091481334237</v>
       </c>
     </row>
     <row r="33">
@@ -5253,46 +5253,46 @@
         <v>4.928124</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>5.013984</v>
+        <v>1.533135</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.629995</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.163115</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.395856</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.395856</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.384093</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.519513</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.519513</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.298895</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>8.5092</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>9.680445000000001</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>7.0432</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>7.0242</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>13.04375</v>
       </c>
     </row>
     <row r="93">
@@ -9676,7 +9676,11 @@
           <t>Share-based payment reserve 20</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -9765,7 +9769,11 @@
           <t>Warrant reserve 19</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -11602,7 +11610,11 @@
           <t>Share-based payment reserve 19</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -11691,7 +11703,11 @@
           <t>Warrant reserve 18</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -12591,7 +12607,11 @@
           <t>Share-based payment reserve 16</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -12680,7 +12700,11 @@
           <t>Warrant reserve 15</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -13582,7 +13606,11 @@
           <t>Share-based payment reserve 17</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -13659,7 +13687,11 @@
           <t>Warrant reserve 16</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -14925,7 +14957,11 @@
           <t>Share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -17803,7 +17839,11 @@
           <t>Share-based payment reserve 15</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -18600,7 +18640,11 @@
           <t>Warrants reserve 16</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -19057,7 +19101,11 @@
           <t>Share-based payment reserve 18</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -20705,7 +20753,11 @@
           <t>Warrants reserve 18 989,895</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -20883,7 +20935,11 @@
           <t>Share-based payment reserve 20 640,100</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -50801,19 +50857,19 @@
         </is>
       </c>
       <c r="O482" s="5" t="n">
-        <v>37.693898</v>
+        <v>-37.693898</v>
       </c>
       <c r="P482" s="5" t="n">
-        <v>19.033361</v>
+        <v>-19.033361</v>
       </c>
       <c r="Q482" s="5" t="n">
-        <v>12.641589</v>
+        <v>-12.641589</v>
       </c>
       <c r="R482" s="5" t="n">
-        <v>14.265394</v>
+        <v>-14.265394</v>
       </c>
       <c r="S482" s="5" t="n">
-        <v>20.806293</v>
+        <v>-20.806293</v>
       </c>
     </row>
     <row r="483">
@@ -54120,10 +54176,10 @@
         </is>
       </c>
       <c r="P520" s="5" t="n">
-        <v>19.033361</v>
+        <v>-19.033361</v>
       </c>
       <c r="Q520" s="5" t="n">
-        <v>12.641589</v>
+        <v>-12.641589</v>
       </c>
       <c r="R520" t="inlineStr">
         <is>
@@ -64496,7 +64552,7 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">

--- a/output/pdf_financials_xlsx/TSK.xlsx
+++ b/output/pdf_financials_xlsx/TSK.xlsx
@@ -879,37 +879,37 @@
         <v>3.600028</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.6730120000000001</v>
+        <v>5.794609</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.481552</v>
+        <v>3.206259</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.724752</v>
+        <v>3.22395</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.654386</v>
+        <v>2.46027</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.636245</v>
+        <v>4.267901</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.958595</v>
+        <v>6.854628</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>3.453764</v>
+        <v>0.9752150000000001</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>1.911807</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>42.051472</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>28.215599</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>14.25439</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>13.937722</v>
@@ -934,31 +934,31 @@
         <v>-2.177678</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1.655645</v>
+        <v>-1.069062</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2.029745</v>
+        <v>-0.469453</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.072786</v>
+        <v>-1.87867</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-1.199539</v>
+        <v>-3.831195</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-2.313292</v>
+        <v>-6.209325</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-2.215393</v>
+        <v>0.263156</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>-1.911807</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0</v>
+        <v>-42.051472</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0</v>
+        <v>-28.215599</v>
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000119</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0.000204</v>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.24682</v>
+        <v>-3.246939</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-1.855195</v>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.24682</v>
+        <v>-3.246939</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.05643</v>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-580.3540946099329</v>
+        <v>-580.3753653108829</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>-36.24873944505044</v>
@@ -2178,22 +2178,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.391639</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.391639</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.940872</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.58203</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.185662</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.268199</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>2.155501</v>
@@ -2282,22 +2282,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.391639</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.391639</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.940872</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.58203</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.185662</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.268199</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>2.155501</v>
@@ -2906,22 +2906,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.135528</v>
+        <v>0.743889</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.467684</v>
+        <v>0.076045</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.971661</v>
+        <v>0.030789</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.357261</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.891195</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.302644</v>
+        <v>0.034445</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>4.001115</v>
@@ -8171,7 +8171,11 @@
           <t>Reclamation deposits 16</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -10342,7 +10346,11 @@
           <t>Reclamation deposits 15</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -11887,7 +11895,11 @@
           <t>Reclamation deposits 12</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -12886,7 +12898,11 @@
           <t>Reclamation deposits 13</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -16761,7 +16777,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -19196,7 +19212,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -21386,7 +21402,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
@@ -23483,7 +23499,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
@@ -32973,7 +32989,11 @@
           <t>Reclamation deposits 13</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -51742,7 +51762,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -64552,7 +64572,7 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -66635,7 +66655,7 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E660" s="5" t="n">
@@ -66728,7 +66748,7 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E661" s="5" t="n">
@@ -69114,7 +69134,7 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E687" s="5" t="n">

--- a/output/pdf_financials_xlsx/TSK.xlsx
+++ b/output/pdf_financials_xlsx/TSK.xlsx
@@ -1921,19 +1921,19 @@
         <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.721624</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>1.248684</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>1.268338</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>1.113562</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.943562</v>
       </c>
     </row>
     <row r="29">
@@ -1973,19 +1973,19 @@
         <v>-2.980453</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>43.173898</v>
+        <v>43.895522</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>27.656361</v>
+        <v>28.905045</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>14.592589</v>
+        <v>15.860927</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>14.763394</v>
+        <v>15.876956</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>20.806293</v>
+        <v>21.749855</v>
       </c>
     </row>
     <row r="30">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>164.8091481334237</v>
+        <v>172.2832161680836</v>
       </c>
     </row>
     <row r="31">
@@ -5651,19 +5651,19 @@
         <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.721624</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>1.248684</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>1.268338</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>1.113562</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.943562</v>
       </c>
     </row>
     <row r="101">
@@ -25966,7 +25966,11 @@
           <t>Depreciation of property, plant and equipment 9</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -29096,7 +29100,11 @@
           <t>Depreciation of property, plant and equipment 8</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -30995,7 +31003,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -51675,7 +51687,11 @@
           <t>Depreciation of property, plant and equipment 8</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
@@ -53235,7 +53251,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D510" t="inlineStr"/>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E510" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TSK.xlsx
+++ b/output/pdf_financials_xlsx/TSK.xlsx
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.059689</v>
+        <v>0.17107</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.196586</v>
+        <v>0.446933</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -1271,16 +1271,16 @@
         <v>-5.912546</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-80.867796</v>
+        <v>5.48</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-46.689722</v>
+        <v>8.622999999999999</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-27.234178</v>
+        <v>1.951</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-29.028788</v>
+        <v>0.498</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-41.612586</v>
@@ -1472,19 +1472,19 @@
         <v>-0.442221</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-0.246365</v>
+        <v>-1.916075</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.627042</v>
+        <v>-1.624023</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>11.533824</v>
+        <v>-4.950348</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-5.423582</v>
+        <v>-0.144129</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-8.872078999999999</v>
+        <v>-2.959533</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-37.693898</v>
@@ -1524,19 +1524,19 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>1.66971</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>3.251065</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>16.484172</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>-5.279453</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>-5.912546</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>0</v>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.003058</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.7987649999999999</v>
+        <v>0.014337</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0.950237</v>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.246939</v>
+        <v>-3.243881</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.05643</v>
+        <v>-1.840858</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.439958</v>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-580.3753653108829</v>
+        <v>-579.8287619200829</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-36.24873944505044</v>
+        <v>-63.16441410915694</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-26.66785934738511</v>
@@ -2087,16 +2087,16 @@
         <v>-199.7796949721459</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>187.307145627666</v>
+        <v>12.69285437233395</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>168.8209160995548</v>
+        <v>31.17908390044518</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>186.6301997541355</v>
+        <v>13.36980024586453</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>196.6267919151924</v>
+        <v>3.373208084807599</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>200</v>
@@ -3930,43 +3930,43 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.379039</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>1.038286</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.546042</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.6253</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.357667</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.479245</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.686404</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>4.525833</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>1.797237</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>3.013347</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>1.280411</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>5.263858</v>
       </c>
     </row>
     <row r="68">
@@ -4110,19 +4110,19 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.301362</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.268134</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.111176</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.234941</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.248584</v>
       </c>
     </row>
     <row r="71">
@@ -4162,19 +4162,19 @@
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.301362</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.268134</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.111176</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.234941</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.248584</v>
       </c>
     </row>
     <row r="72">
@@ -4370,13 +4370,13 @@
         <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.461037</v>
+        <v>0.159675</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.382502</v>
+        <v>0.114368</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.121023</v>
+        <v>0.009847</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>0</v>
@@ -4645,30 +4645,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L80" s="3" t="n">
+        <v>0.01328057977965824</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>0.01332825455855743</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.009721854707696386</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.2005683913619538</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.007239937506522115</v>
       </c>
     </row>
     <row r="81">
@@ -6388,7 +6378,7 @@
         <v>0</v>
       </c>
       <c r="O114" s="3" t="n">
-        <v>0</v>
+        <v>-2.007562</v>
       </c>
       <c r="P114" s="3" t="n">
         <v>0</v>
@@ -8721,7 +8711,11 @@
           <t>Current portion of lease obligation 12</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10801,7 +10795,11 @@
           <t>Current portion of lease obligation 11</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -26913,7 +26911,11 @@
           <t>Issue of shares pursuant to private placement 17</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -29460,7 +29462,11 @@
           <t>Purchase of marketable securities 7</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -29733,7 +29739,11 @@
           <t>Issue of shares pursuant to private placement 16</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -31824,7 +31834,11 @@
           <t>Issue of shares pursuant to private placement 13</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -33278,7 +33292,11 @@
           <t>Issue of shares pursuant to private placement 14</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -42671,7 +42689,11 @@
           <t>Shares issued - private placement</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -43935,7 +43957,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -45482,7 +45508,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E423" s="5" t="n">
         <v>1.06301</v>
       </c>
@@ -48058,7 +48088,11 @@
           <t>Private placements 1,063,010</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E451" s="5" t="n">
         <v>0.34</v>
       </c>
@@ -50746,7 +50780,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
           <t>-</t>
@@ -52739,7 +52777,11 @@
           <t>Income tax recovery 25</t>
         </is>
       </c>
-      <c r="D504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E504" t="inlineStr">
         <is>
           <t>-</t>
@@ -54066,7 +54108,11 @@
           <t>Income tax recovery 22</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E519" t="inlineStr">
         <is>
           <t>-</t>
@@ -56214,7 +56260,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D543" t="inlineStr"/>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E543" t="inlineStr">
         <is>
           <t>-</t>
@@ -56297,7 +56347,11 @@
           <t>Loss from discontinued operations 19</t>
         </is>
       </c>
-      <c r="D544" t="inlineStr"/>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E544" t="inlineStr">
         <is>
           <t>-</t>
@@ -58231,7 +58285,11 @@
           <t>Income from discontinued operations 21</t>
         </is>
       </c>
-      <c r="D566" t="inlineStr"/>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E566" t="inlineStr">
         <is>
           <t>-</t>
@@ -61247,7 +61305,11 @@
           <t>Income from discontinued operations 19</t>
         </is>
       </c>
-      <c r="D600" t="inlineStr"/>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E600" t="inlineStr">
         <is>
           <t>-</t>
@@ -66046,7 +66108,11 @@
           <t>General and office expenses</t>
         </is>
       </c>
-      <c r="D653" t="inlineStr"/>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E653" s="5" t="n">
         <v>0.111381</v>
       </c>
@@ -66406,7 +66472,11 @@
           <t>Amortization expense</t>
         </is>
       </c>
-      <c r="D657" t="inlineStr"/>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E657" s="5" t="n">
         <v>0.003058</v>
       </c>
@@ -68509,7 +68579,11 @@
           <t>General and office expenses 111,381</t>
         </is>
       </c>
-      <c r="D680" t="inlineStr"/>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E680" s="5" t="n">
         <v>0.184901</v>
       </c>
@@ -68877,7 +68951,11 @@
           <t>Amortization expense 3,058</t>
         </is>
       </c>
-      <c r="D684" t="inlineStr"/>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E684" s="5" t="n">
         <v>0.005478</v>
       </c>
@@ -69615,7 +69693,11 @@
           <t>Income tax recovery (expenses) (Note 14) 7,676</t>
         </is>
       </c>
-      <c r="D692" t="inlineStr"/>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E692" s="5" t="n">
         <v>-0.008337000000000001</v>
       </c>
